--- a/game-stats/Week5_PAK-LIONS_vs_K2.xlsx
+++ b/game-stats/Week5_PAK-LIONS_vs_K2.xlsx
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>No Name</t>
+          <t>Terryon Taylor</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
